--- a/artfynd/A 60135-2022 artfynd.xlsx
+++ b/artfynd/A 60135-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60135-2022 artfynd.xlsx
+++ b/artfynd/A 60135-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2625,6 +2625,594 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114912252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Håvaberget (Håvaberget), Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>508073</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6821950</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114912402</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Håvaberget (Håven), Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>508133</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6822043</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114912335</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78196</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Håvaberget (Håvaberget), Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>508141</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6822022</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114912428</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Håvaberget (Håvaberget), Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>508131</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6822019</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114912264</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Håvaberget (Håven), Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>508074</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6821950</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
